--- a/docs/kriteria.xlsx
+++ b/docs/kriteria.xlsx
@@ -756,6 +756,7 @@
       <c r="C7" s="1">
         <v>1</v>
       </c>
+      <c r="D7" s="2"/>
     </row>
     <row r="8" ht="15">
       <c r="A8" s="1" t="s">

--- a/docs/kriteria.xlsx
+++ b/docs/kriteria.xlsx
@@ -9,9 +9,6 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <calcPr/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
-  </extLst>
 </workbook>
 </file>
 

--- a/docs/kriteria.xlsx
+++ b/docs/kriteria.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <calcPr/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+  </extLst>
 </workbook>
 </file>
 
@@ -820,6 +823,7 @@
       <c r="C13" s="1">
         <v>2</v>
       </c>
+      <c r="D13" s="2"/>
     </row>
     <row r="14" ht="15">
       <c r="A14" s="1" t="s">
@@ -831,6 +835,7 @@
       <c r="C14" s="1">
         <v>2</v>
       </c>
+      <c r="D14" s="2"/>
     </row>
     <row r="15" ht="15">
       <c r="A15" s="1" t="s">
@@ -842,6 +847,7 @@
       <c r="C15" s="1">
         <v>2</v>
       </c>
+      <c r="D15" s="2"/>
     </row>
     <row r="16" ht="15">
       <c r="A16" s="1" t="s">
